--- a/AAII_Financials/Quarterly/USCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>USCB</t>
   </si>
@@ -656,217 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E8" s="3">
         <v>25400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13700</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>13100</v>
       </c>
       <c r="Z8" s="3">
         <v>13100</v>
       </c>
       <c r="AA8" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>13300</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -951,53 +958,56 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E10" s="3">
         <v>25400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,8 +1082,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1155,8 +1169,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,8 +1258,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1285,8 +1305,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1327,8 +1347,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1345,16 +1368,16 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1369,11 +1392,11 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,61 +1468,62 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E17" s="3">
         <v>13200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10100</v>
-      </c>
-      <c r="O17" s="3">
-        <v>10000</v>
       </c>
       <c r="P17" s="3">
         <v>10000</v>
       </c>
       <c r="Q17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1000</v>
       </c>
       <c r="U17" s="3">
         <v>1000</v>
@@ -1505,117 +1532,123 @@
         <v>1000</v>
       </c>
       <c r="W17" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="X17" s="3">
         <v>1100</v>
       </c>
       <c r="Y17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4100</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E18" s="3">
         <v>12200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9200</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,16 +1679,17 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>400</v>
       </c>
       <c r="F20" s="3">
         <v>400</v>
@@ -1670,13 +1704,13 @@
         <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K20" s="3">
         <v>500</v>
       </c>
       <c r="L20" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
@@ -1685,130 +1719,133 @@
         <v>400</v>
       </c>
       <c r="O20" s="3">
+        <v>400</v>
+      </c>
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E21" s="3">
         <v>11900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>9300</v>
       </c>
       <c r="J21" s="3">
         <v>9300</v>
       </c>
       <c r="K21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L21" s="3">
         <v>8300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5500</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,8 +1855,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1862,8 +1902,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1904,180 +1944,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1900</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2200</v>
       </c>
       <c r="J24" s="3">
         <v>2200</v>
       </c>
       <c r="K24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1300</v>
       </c>
       <c r="O24" s="3">
         <v>1300</v>
       </c>
       <c r="P24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E26" s="3">
         <v>9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>6900</v>
       </c>
       <c r="J26" s="3">
         <v>6900</v>
       </c>
       <c r="K26" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L26" s="3">
         <v>6200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E27" s="3">
         <v>9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>6900</v>
       </c>
       <c r="J27" s="3">
         <v>6900</v>
       </c>
       <c r="K27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L27" s="3">
         <v>6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-83500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,16 +2745,19 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-400</v>
       </c>
       <c r="F32" s="3">
         <v>-400</v>
@@ -2702,13 +2772,13 @@
         <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="K32" s="3">
         <v>-500</v>
       </c>
       <c r="L32" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
@@ -2717,141 +2787,147 @@
         <v>-400</v>
       </c>
       <c r="O32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7200</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E33" s="3">
         <v>9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>6900</v>
       </c>
       <c r="J33" s="3">
         <v>6900</v>
       </c>
       <c r="K33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L33" s="3">
         <v>6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-83500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>700</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E35" s="3">
         <v>9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>6900</v>
       </c>
       <c r="J35" s="3">
         <v>6900</v>
       </c>
       <c r="K35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L35" s="3">
         <v>6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-83500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>700</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,80 +3263,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E41" s="3">
         <v>79000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>54800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>98000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>87300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>63300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,80 +3350,83 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E42" s="3">
         <v>8900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4900</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>5600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>55500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>74500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>83100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>84900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>43300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>62400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>42900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>100500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>41100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3439,11 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3393,8 +3486,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3479,8 +3575,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3521,53 +3617,56 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E45" s="3">
         <v>11800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3607,53 +3706,56 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E46" s="3">
         <v>99700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>79000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>117000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>95200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>57000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>95200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>143900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>56600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>100900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>76100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3693,53 +3795,56 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>482400</v>
+      </c>
+      <c r="E47" s="3">
         <v>431600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>470800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>482900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>451100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>443900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>434300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>433800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>411600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>438600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>414500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>422200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>444100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>422000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -3779,80 +3884,83 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E48" s="3">
         <v>9200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>18700</v>
       </c>
       <c r="T48" s="3">
         <v>18700</v>
       </c>
       <c r="U48" s="3">
+        <v>18700</v>
+      </c>
+      <c r="V48" s="3">
         <v>19500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,79 +4240,82 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E52" s="3">
         <v>70800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>69300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>69500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>66800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>60300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>61500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>65400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>45800</v>
       </c>
       <c r="P52" s="3">
         <v>45800</v>
       </c>
       <c r="Q52" s="3">
+        <v>45800</v>
+      </c>
+      <c r="R52" s="3">
         <v>42400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>38900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>34900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>38500</v>
-      </c>
-      <c r="X52" s="3">
-        <v>39200</v>
       </c>
       <c r="Y52" s="3">
         <v>39200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>39200</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,80 +4418,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3019700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2845700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2791500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2767900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2719500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2677400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2581200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2504000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2458300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2489100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2339100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2244600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2225900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2163800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2085800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2037500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2016100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1967300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1853900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1755000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1667000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1633400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1501700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,53 +4575,54 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2452300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2493600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2345100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2455600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2335700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2309600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2174000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2126600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2056700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2102800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1937100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1920900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1921300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1830500</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -4531,53 +4662,56 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E58" s="3">
         <v>50800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>159400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>35300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>67900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>114000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>87700</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4617,8 +4751,11 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4661,36 +4798,36 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>23100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>32500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>24800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20800</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,53 +4840,56 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2703100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2546900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2508500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2468900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2398800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2339900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2244000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2152100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2081500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2126200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2052500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1947100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1932100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1918700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4789,53 +4929,56 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E61" s="3">
         <v>55100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>89000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>95700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>110500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>111200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>156900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>157700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>88400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>89200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>94900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4875,53 +5018,56 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E62" s="3">
         <v>20500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>16600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10600</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,80 +5374,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2786500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2622500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2574400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2558900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2487900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2452300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2365800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2290000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2257300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2294100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2147100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2061700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2042200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1980000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1903400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1860000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1836000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1775200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1650000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1553100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1500700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1462900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1330700</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5572,16 +5740,16 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>24600</v>
-      </c>
-      <c r="X70" s="3">
-        <v>32100</v>
       </c>
       <c r="Y70" s="3">
         <v>32100</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>32100</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,80 +5852,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-49500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-49100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-62200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-67800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-73800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-85000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-88500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-91300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-95100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-99600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-104100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-108500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-114100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-119400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-124200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-129900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-46400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,80 +6208,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>233200</v>
+      </c>
+      <c r="E76" s="3">
         <v>223200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>217200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>209100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>231600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>225100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>215400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>213900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>201000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>195000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>192000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>182900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>183700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>183900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>182400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>180100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>192000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>203900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>201900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>141700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>138300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>138900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E81" s="3">
         <v>9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>6900</v>
       </c>
       <c r="J81" s="3">
         <v>6900</v>
       </c>
       <c r="K81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L81" s="3">
         <v>6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-83500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>700</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,22 +6604,23 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -6436,7 +6635,7 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -6469,7 +6668,7 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
@@ -6478,11 +6677,11 @@
         <v>300</v>
       </c>
       <c r="Z83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>900</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,83 +7136,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E89" s="3">
         <v>15300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1600</v>
-      </c>
-      <c r="V89" s="3">
-        <v>9800</v>
       </c>
       <c r="W89" s="3">
         <v>9800</v>
       </c>
       <c r="X89" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Y89" s="3">
         <v>4100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14500</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7008,8 +7225,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,28 +7260,29 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -7073,50 +7294,50 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
       <c r="X91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7126,8 +7347,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,83 +7525,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-132100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-43500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-51000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-74900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-66500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-82700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-76800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-69800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-80800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-80700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-127400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-61100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-94900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-75900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-143300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7384,8 +7614,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7425,10 +7659,10 @@
         <v>2300</v>
       </c>
       <c r="E96" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F96" s="3">
         <v>1800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>2000</v>
       </c>
       <c r="G96" s="3">
         <v>2000</v>
@@ -7437,10 +7671,10 @@
         <v>2000</v>
       </c>
       <c r="I96" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J96" s="3">
         <v>900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1000</v>
       </c>
       <c r="K96" s="3">
         <v>1000</v>
@@ -7448,8 +7682,8 @@
       <c r="L96" s="3">
         <v>1000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
+      <c r="M96" s="3">
+        <v>1000</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>3</v>
@@ -7460,8 +7694,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,83 +8003,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E100" s="3">
         <v>40200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>35200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>24300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>78500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>92500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-47400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>143900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>96300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>57100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>69300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>52600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>17900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>55400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>105700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>73800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>26300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>130000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>15000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>162700</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7846,8 +8092,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7890,8 +8139,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7932,83 +8181,86 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E102" s="3">
         <v>40500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>38500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-53800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>47900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-23400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-58800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>58200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-129700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>141700</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8016,6 +8268,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
